--- a/v5_data/latest/market_review.xlsx
+++ b/v5_data/latest/market_review.xlsx
@@ -27726,12 +27726,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27741,37 +27741,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sina+eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sina</t>
-        </is>
-      </c>
+          <t>legulegu_fallback+eastmoney_public_pool</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>5571</v>
+        <v>5213</v>
       </c>
       <c r="G2" t="n">
-        <v>2566</v>
+        <v>2345</v>
       </c>
       <c r="H2" t="n">
-        <v>2824</v>
+        <v>2713</v>
       </c>
       <c r="I2" t="n">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="J2" t="n">
         <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4605995332974331</v>
+        <v>0.4498369460962977</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5069107880093341</v>
+        <v>0.5204296949932861</v>
       </c>
       <c r="M2" t="n">
-        <v>-258</v>
+        <v>-368</v>
       </c>
       <c r="N2" t="n">
         <v>52</v>
@@ -27835,7 +27831,7 @@
         </is>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -27872,15 +27868,9 @@
       <c r="AP2" t="n">
         <v>12</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>148</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>131</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1449854302288</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
           <t>上涨/下跌/平盘由逐股快照计数；涨停/跌停读取东方财富公开池；炸板、封板率、昨日涨停溢价、连板高度为影子情绪层，仅记录和QA，暂不改变推荐。乐咕只做交叉核验。</t>
@@ -27942,12 +27932,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27974,12 +27964,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -28006,12 +27996,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28038,12 +28028,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28070,12 +28060,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -28102,12 +28092,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28134,12 +28124,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28166,12 +28156,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -28198,12 +28188,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -28230,12 +28220,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -28262,12 +28252,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -28294,12 +28284,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -28326,12 +28316,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -28358,12 +28348,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -28390,12 +28380,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -28422,12 +28412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -28454,12 +28444,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -28486,12 +28476,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -28518,12 +28508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -28550,12 +28540,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -28582,12 +28572,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -28614,12 +28604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -28646,12 +28636,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -28678,12 +28668,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -28710,12 +28700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -28742,12 +28732,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -28774,12 +28764,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -28806,12 +28796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -28838,12 +28828,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -28870,12 +28860,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -28902,12 +28892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -28934,12 +28924,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -28966,12 +28956,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -28998,12 +28988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -29030,12 +29020,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -29062,12 +29052,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -29094,12 +29084,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -29126,12 +29116,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -29158,12 +29148,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -29190,12 +29180,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -29222,12 +29212,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -29254,12 +29244,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -29286,12 +29276,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -29318,12 +29308,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -29350,12 +29340,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -29382,12 +29372,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -29414,12 +29404,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -29446,12 +29436,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -29478,12 +29468,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -29510,12 +29500,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -29542,12 +29532,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -29574,12 +29564,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -29606,12 +29596,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -29638,12 +29628,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -29670,12 +29660,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -29702,12 +29692,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -29734,12 +29724,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -29766,12 +29756,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -29798,12 +29788,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -29830,12 +29820,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -29862,12 +29852,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -29894,12 +29884,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -29926,12 +29916,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -29958,12 +29948,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -29990,12 +29980,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -30022,12 +30012,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -30054,12 +30044,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -30086,12 +30076,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -30118,12 +30108,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -30150,12 +30140,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -30182,12 +30172,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -30214,12 +30204,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -30246,12 +30236,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -30278,12 +30268,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -30310,12 +30300,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -30342,12 +30332,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -30374,12 +30364,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -30406,12 +30396,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -30438,12 +30428,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -30470,12 +30460,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -30502,12 +30492,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -30534,12 +30524,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -30566,12 +30556,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -30598,12 +30588,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -30630,12 +30620,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -30662,12 +30652,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -30694,12 +30684,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -30726,12 +30716,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -30758,12 +30748,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -30790,12 +30780,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -30822,12 +30812,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -30854,12 +30844,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -30886,12 +30876,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -30918,12 +30908,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -30950,12 +30940,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -30982,12 +30972,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -31014,12 +31004,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -31046,12 +31036,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -31078,12 +31068,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -31110,12 +31100,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -31142,12 +31132,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -31174,12 +31164,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -31206,12 +31196,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -31238,12 +31228,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -31270,12 +31260,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -31302,12 +31292,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -31334,12 +31324,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -31366,12 +31356,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -31398,12 +31388,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -31430,12 +31420,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -31462,12 +31452,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -31494,12 +31484,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -31526,12 +31516,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -31558,12 +31548,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -31590,12 +31580,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -31622,12 +31612,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -31654,12 +31644,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -31686,12 +31676,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -31718,12 +31708,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -31750,12 +31740,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -31782,12 +31772,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -31814,12 +31804,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -31846,12 +31836,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -31878,12 +31868,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -31910,12 +31900,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -31942,12 +31932,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -31974,12 +31964,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -32006,12 +31996,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -32038,12 +32028,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -32070,12 +32060,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -32102,12 +32092,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -32134,12 +32124,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -32166,12 +32156,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -32198,12 +32188,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -32230,12 +32220,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -32262,12 +32252,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -32294,12 +32284,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -32326,12 +32316,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -32358,12 +32348,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -32390,12 +32380,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -32422,12 +32412,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -32454,12 +32444,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -32486,12 +32476,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -32518,12 +32508,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -32550,12 +32540,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -32582,12 +32572,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -32614,12 +32604,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -32646,12 +32636,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -32678,12 +32668,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -32710,12 +32700,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -32742,12 +32732,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -32774,12 +32764,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -32806,12 +32796,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -32838,12 +32828,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -32870,12 +32860,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -32902,12 +32892,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -32934,12 +32924,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -32966,12 +32956,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -32998,12 +32988,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -33030,12 +33020,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -33062,12 +33052,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -33094,12 +33084,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -33126,12 +33116,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -33158,12 +33148,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -33190,12 +33180,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -33222,12 +33212,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -33254,12 +33244,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -33286,12 +33276,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -33318,12 +33308,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -33350,12 +33340,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -33382,12 +33372,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -33414,12 +33404,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -33446,12 +33436,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -33478,12 +33468,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -33510,12 +33500,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -33542,12 +33532,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -33574,12 +33564,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -33606,12 +33596,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -33638,12 +33628,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -33670,12 +33660,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -33702,12 +33692,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -33734,12 +33724,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -33766,12 +33756,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -33798,12 +33788,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -33830,12 +33820,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -33862,12 +33852,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -33894,12 +33884,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -33926,12 +33916,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -33958,12 +33948,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33990,12 +33980,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -34022,12 +34012,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -34054,12 +34044,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -34086,12 +34076,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -34118,12 +34108,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -34150,12 +34140,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -34182,12 +34172,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -34214,12 +34204,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -34246,12 +34236,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34278,12 +34268,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -34310,12 +34300,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -34342,12 +34332,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -34374,12 +34364,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -34406,12 +34396,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -34438,12 +34428,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -34470,12 +34460,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -34502,12 +34492,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -34534,12 +34524,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -34566,12 +34556,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -34598,12 +34588,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -34630,12 +34620,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -34662,12 +34652,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -34694,12 +34684,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -34726,12 +34716,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -34758,12 +34748,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -34790,12 +34780,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -34822,12 +34812,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -34854,12 +34844,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -34886,12 +34876,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -34918,12 +34908,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -34950,12 +34940,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -34982,12 +34972,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -35014,12 +35004,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -35046,12 +35036,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -35078,12 +35068,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -35110,12 +35100,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -35142,12 +35132,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -35174,12 +35164,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -35206,12 +35196,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -35238,12 +35228,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -35270,12 +35260,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -35302,12 +35292,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -35334,12 +35324,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -35366,12 +35356,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -35398,12 +35388,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -35430,12 +35420,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -35462,12 +35452,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -35494,12 +35484,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -35526,12 +35516,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -35558,12 +35548,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -35590,12 +35580,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -35622,12 +35612,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -35654,12 +35644,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -35686,12 +35676,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -35718,12 +35708,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -35750,12 +35740,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -35782,12 +35772,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -35814,12 +35804,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -35846,12 +35836,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -35878,12 +35868,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -35910,12 +35900,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -35942,12 +35932,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -35974,12 +35964,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -36006,12 +35996,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -36038,12 +36028,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -36070,12 +36060,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -36102,12 +36092,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -36134,12 +36124,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -36166,12 +36156,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -36198,12 +36188,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -36230,12 +36220,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -36262,12 +36252,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -36294,12 +36284,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -36326,12 +36316,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -36358,12 +36348,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -36390,12 +36380,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -36422,12 +36412,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -36454,12 +36444,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -36486,12 +36476,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -36518,12 +36508,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -36550,12 +36540,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -36582,12 +36572,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -36614,12 +36604,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -36646,12 +36636,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -36678,12 +36668,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -36710,12 +36700,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -36742,12 +36732,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -36774,12 +36764,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -36806,12 +36796,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -36838,12 +36828,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -36870,12 +36860,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -36902,12 +36892,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -36934,12 +36924,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -36966,12 +36956,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -36998,12 +36988,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -37030,12 +37020,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -37062,12 +37052,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -37094,12 +37084,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -37126,12 +37116,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -37158,12 +37148,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -37190,12 +37180,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -37222,12 +37212,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -37254,12 +37244,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -37286,12 +37276,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -37318,12 +37308,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -37350,12 +37340,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -37382,12 +37372,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -37414,12 +37404,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -37446,12 +37436,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -37478,12 +37468,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -37510,12 +37500,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -37542,12 +37532,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -37574,12 +37564,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -37606,12 +37596,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -37638,12 +37628,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -37670,12 +37660,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -37702,12 +37692,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -37734,12 +37724,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -37766,12 +37756,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -37798,12 +37788,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -37830,12 +37820,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -37862,12 +37852,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -37894,12 +37884,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -37926,12 +37916,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -37958,12 +37948,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -37990,12 +37980,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -38022,12 +38012,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -38054,12 +38044,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -38086,12 +38076,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -38118,12 +38108,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -38150,12 +38140,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -38182,12 +38172,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -38214,12 +38204,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -38246,12 +38236,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -38278,12 +38268,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -38310,12 +38300,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -38342,12 +38332,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -38374,12 +38364,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -38406,12 +38396,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -38438,12 +38428,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-06 20:01:13+0800</t>
+          <t>2026-10-08 02:11:56+0800</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -38478,7 +38468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41704,7 +41694,7 @@
         <v>1.24432631333669</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4912280701754386</v>
+        <v>0.4912280701754385</v>
       </c>
       <c r="W19" t="n">
         <v>4.798619727293651</v>
@@ -41799,6 +41789,171 @@
         <v>9</v>
       </c>
       <c r="AW19" t="inlineStr">
+        <is>
+          <t>盘后</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:11:56+0800</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>legulegu_fallback+eastmoney_public_pool</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>5213</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2345</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2713</v>
+      </c>
+      <c r="I20" t="n">
+        <v>155</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4498369460962977</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5204296949932861</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-368</v>
+      </c>
+      <c r="N20" t="n">
+        <v>52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>64</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>57</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.24432631333669</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.798619727293651</v>
+      </c>
+      <c r="X20" t="n">
+        <v>199</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>000011|000504|000678|000692|000710|001206|001266|001318|002041|002058|002164|002188|002226|002242|002316|002388|002419|002454|002755|002866|002962|300893|301190|600059|600072|600081|600131|600241|600356|600592|600663|600825|601118|603127|603185|603188|603200|603538|603590|603739|603906|603919|603928|603948|605011|605287|605288|605303|605388|605577|688185|688806</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>001216|001234|600156|603797|603949|605058|605162|605258|920202</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>000668|002043|002262|002273|002513|002799|600418|600719|603396|603400|603982|688265</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>000002|000011|000036|000068|000607|000678|000823|002058|002074|002205|002242|002244|002303|002494|002799|002815|002846|002866|002882|002912|002913|301190|301513|301560|600032|600152|600189|600241|600325|600488|600657|600825|600982|601238|601519|601811|601949|603188|603200|603322|603328|603400|603533|603598|603602|603630|603636|603949|603980|605058|605198|605258|605303|605388|688655|688685|920779</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>000002|000011|000031|000069|000498|000504|000513|000514|000678|000710|000739|000897|000910|001201|001211|001216|001217|001228|001234|001318|001914|002058|002074|002099|002164|002188|002205|002238|002242|002244|002259|002262|002303|002363|002382|002388|002419|002434|002454|002482|002513|002614|002708|002799|002833|002866|002882|002912|002913|002962|002988|003006|300171|300211|300239|300358|300417|300461|300489|300514|300523|300549|300647|300685|300713|300725|300746|300787|300800|300804|300850|300851|300904|300909|300917|300981|301010|301017|301037|301047|301080|301108|301125|301135|301166|301170|301190|301207|301218|301226|301258|301311|301320|301355|301359|301529|301550|301560|600007|600023|600027|600032|600059|600064|600072|600081|600152|600177|600189|600202|600241|600377|600383|600418|600488|600583|600592|600638|600648|600663|600674|600719|600802|600825|600886|600901|600982|601018|601107|601218|601238|601298|601328|601398|601811|601988|603037|603048|603073|603170|603172|603188|603200|603230|603231|603235|603238|603266|603278|603396|603400|603500|603529|603578|603602|603626|603636|603657|603727|603739|603768|603798|603886|603949|603967|603968|603982|605058|605122|605303|605369|605388|688029|688030|688058|688067|688075|688105|688137|688139|688162|688185|688193|688228|688238|688265|688317|688329|688370|688393|688468|688517|688560|688638|688639|688710|920066|920779|920982</t>
+        </is>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:00:00</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>2345</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2713</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>155</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>上涨/下跌/平盘由逐股快照计数；涨停/跌停读取东方财富公开池；炸板、封板率、昨日涨停溢价、连板高度为影子情绪层，仅记录和QA，暂不改变推荐。乐咕只做交叉核验。</t>
+        </is>
+      </c>
+      <c r="AU20" t="n">
+        <v>52</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW20" t="inlineStr">
         <is>
           <t>盘后</t>
         </is>
@@ -42083,11 +42238,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -42095,124 +42250,124 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4605995332974331</v>
+        <v>0.4498369460962977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2914184988146745</v>
+        <v>-0.01076258720113538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4145018492140929</v>
+        <v>0.3414570170099161</v>
       </c>
       <c r="G2" t="n">
         <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4123216666550544</v>
+        <v>0.4142961550466988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4123216666550544</v>
+        <v>0.4142961550466988</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5069107880093341</v>
+        <v>0.5204296949932861</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3041524303814706</v>
+        <v>0.01351890698395197</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5607126637446787</v>
+        <v>0.6311537429302517</v>
       </c>
       <c r="O2" t="n">
         <v>0.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5632674201951666</v>
+        <v>0.5610128030792781</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5632674201951666</v>
+        <v>0.5610128030792781</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="T2" t="n">
-        <v>-258</v>
+        <v>-368</v>
       </c>
       <c r="U2" t="n">
-        <v>3316</v>
+        <v>-110</v>
       </c>
       <c r="V2" t="n">
-        <v>-814.6</v>
+        <v>-1608</v>
       </c>
       <c r="W2" t="n">
         <v>0.8</v>
       </c>
       <c r="X2" t="n">
-        <v>-811.6666666666666</v>
+        <v>-788.3157894736842</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="Z2" t="n">
-        <v>-811.6666666666666</v>
+        <v>-788.3157894736842</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="AB2" t="n">
         <v>52</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>60</v>
+        <v>49.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>56.38888888888889</v>
+        <v>56.1578947368421</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AH2" t="n">
-        <v>56.38888888888889</v>
+        <v>56.1578947368421</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AJ2" t="n">
         <v>9</v>
       </c>
       <c r="AK2" t="n">
-        <v>-47</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>16.6</v>
+        <v>18</v>
       </c>
       <c r="AM2" t="n">
         <v>0.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.22222222222222</v>
+        <v>12.05263157894737</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.22222222222222</v>
+        <v>12.05263157894737</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.5</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="AR2" t="n">
         <v>1449854302288</v>
@@ -42253,7 +42408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42585,7 +42740,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -42594,63 +42749,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5571</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>有效涨跌幅=5571; 尝试次数=2; 前序错误=第1次:TimeoutError:upstream call exceeded 45s</t>
+          <t>尝试次数=2; 第1次:ConnectTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Max retries exceeded with url: /quotes_service/api/json_v2.php/Market_Center.getHQNodeData?page=54&amp;num=80&amp;sort=symbol&amp;asc=1&amp;node=hs_a&amp;symbol=&amp;_s_r_a=page (Caused by ConnectTimeoutError(&lt;HTTPConnection(host='vip.stock.finance.sina.com.cn', port=80) at 0x7fca27922cd0&gt;, 'Connection to vip.stock.finance.sina.com.cn timed out. (connect timeout=15)')) | 第2次:ConnectTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Max retries exceeded with url: /quotes_service/api/json_v2.php/Market_Center.getHQNodeData?page=59&amp;num=80&amp;sort=symbol&amp;asc=1&amp;node=hs_a&amp;symbol=&amp;_s_r_a=page (Caused by ConnectTimeoutError(&lt;HTTPConnection(host='vip.stock.finance.sina.com.cn', port=80) at 0x7fca279aa890&gt;, 'Connection to vip.stock.finance.sina.com.cn timed out. (connect timeout=15)'))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>全市场逐股快照正式源</t>
+          <t>正式口径与乐咕差异</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>警告</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>legulegu_fallback+eastmoney_public_pool</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5571</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>按有效涨跌幅覆盖数择优</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>正式口径与乐咕差异</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>sina+eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>上涨:正式2566/乐咕2345 | 下跌:正式2824/乐咕2713 | 平盘:正式181/乐咕155 | 涨停:正式52/乐咕56 | 跌停:正式9/乐咕12</t>
+          <t>涨停:正式52/乐咕56 | 跌停:正式9/乐咕12</t>
         </is>
       </c>
     </row>
